--- a/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
+++ b/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="41.800000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="20.900000000000002"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,21 +175,21 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Sunday, September 27, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>13:00 EDT</t>
+          <t>15:00 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn Fc 2014/2015</t>
+          <t>SkillsU FC U12</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -199,12 +199,12 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>SkillsU FC U12</t>
+          <t>DV7 NY B2014/15</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Bush Terminal Park - Bush Terminal #2 11v11</t>
+          <t>Shore Road Park - Turf - Soccer Turf - Field 02</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,27 +214,27 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Sunday, October 18, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>15:00 EDT</t>
+          <t>12:15 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>SkillsU FC U12</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 White</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -244,12 +244,12 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>DV7 NY B2014/15</t>
+          <t>SkillsU FC U12</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Shore Road Park - Turf - Soccer Turf - Field 02</t>
+          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,27 +259,27 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 18, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>12:15 EDT</t>
+          <t>15:45 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 White</t>
+          <t>SkillsU FC U12</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>SkillsU FC U12</t>
+          <t>Brooklyn City FC F.C. B14/15 Blue</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+          <t>Shore Road Park - Turf - Soccer Turf - Field 02</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,17 +304,17 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn City FC F.C. B14/15 Blue</t>
+          <t>South Brooklyn Fc 2014/2015</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
@@ -355,21 +355,21 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>15:45 EDT</t>
+          <t>18:00 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>SkillsU FC U12</t>
+          <t>DV7 NY B2014/15</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn Fc 2014/2015</t>
+          <t>SkillsU FC U12</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Shore Road Park - Turf - Soccer Turf - Field 02</t>
+          <t>St. Michael’s Playground  - Full Field 11v11</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,27 +394,27 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Saturday, November 14, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>18:00 EST</t>
+          <t>14:15 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>DV7 NY B2014/15</t>
+          <t>SkillsU FC U12</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>SkillsU FC U12</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 White</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>St. Michael’s Playground  - Full Field 11v11</t>
+          <t>Shore Road Park - Turf - Soccer Turf - Field 02</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -439,27 +439,27 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Sunday, November 22, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>14:15 EST</t>
+          <t>18:00 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>SkillsU FC U12</t>
+          <t>South Brooklyn Fc 2014/2015</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 White</t>
+          <t>SkillsU FC U12</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Shore Road Park - Turf - Soccer Turf - Field 02</t>
+          <t>Leif Ericson Park - Dust Bowl - Dust Bowl Field </t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
+++ b/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
@@ -194,7 +194,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 - 6</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
+++ b/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>15:45 EDT</t>
+          <t>15:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
+++ b/data/2026/cjsl/fall/skillsu-fc-u12.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 3</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
